--- a/shared/src/commonMain/resources/pattern.xlsx
+++ b/shared/src/commonMain/resources/pattern.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\intelijIdea\TermoGramm\shared\src\commonMain\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A394B07-4AE1-42CC-9A93-F825C0651B60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3927476-F2F9-49D0-830C-E07CAD0FBF13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1995" yWindow="4770" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -330,43 +330,43 @@
     <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" textRotation="90"/>
     </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" textRotation="90"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" textRotation="90"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" textRotation="90"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -758,308 +758,308 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:76" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="11"/>
-      <c r="I1" s="11"/>
-      <c r="J1" s="11"/>
-      <c r="K1" s="11"/>
-      <c r="AD1" s="18" t="s">
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="16"/>
+      <c r="AD1" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="AE1" s="12"/>
-      <c r="AF1" s="12"/>
-      <c r="AG1" s="12"/>
-      <c r="AH1" s="12"/>
-      <c r="AI1" s="12"/>
-      <c r="AJ1" s="12"/>
-      <c r="AK1" s="12"/>
-      <c r="AL1" s="12"/>
-      <c r="AM1" s="12"/>
-      <c r="AN1" s="12"/>
-      <c r="AO1" s="12"/>
-      <c r="AP1" s="12"/>
-      <c r="AQ1" s="12"/>
-      <c r="AR1" s="12"/>
-      <c r="AS1" s="12"/>
-      <c r="AT1" s="12"/>
-      <c r="BJ1" s="6" t="s">
+      <c r="AE1" s="18"/>
+      <c r="AF1" s="18"/>
+      <c r="AG1" s="18"/>
+      <c r="AH1" s="18"/>
+      <c r="AI1" s="18"/>
+      <c r="AJ1" s="18"/>
+      <c r="AK1" s="18"/>
+      <c r="AL1" s="18"/>
+      <c r="AM1" s="18"/>
+      <c r="AN1" s="18"/>
+      <c r="AO1" s="18"/>
+      <c r="AP1" s="18"/>
+      <c r="AQ1" s="18"/>
+      <c r="AR1" s="18"/>
+      <c r="AS1" s="18"/>
+      <c r="AT1" s="18"/>
+      <c r="BJ1" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="BK1" s="6"/>
-      <c r="BL1" s="6"/>
-      <c r="BM1" s="6"/>
-      <c r="BN1" s="6"/>
-      <c r="BO1" s="6"/>
-      <c r="BP1" s="6"/>
-      <c r="BQ1" s="6"/>
-      <c r="BR1" s="6"/>
-      <c r="BS1" s="6"/>
-      <c r="BT1" s="6"/>
-      <c r="BU1" s="6"/>
+      <c r="BK1" s="14"/>
+      <c r="BL1" s="14"/>
+      <c r="BM1" s="14"/>
+      <c r="BN1" s="14"/>
+      <c r="BO1" s="14"/>
+      <c r="BP1" s="14"/>
+      <c r="BQ1" s="14"/>
+      <c r="BR1" s="14"/>
+      <c r="BS1" s="14"/>
+      <c r="BT1" s="14"/>
+      <c r="BU1" s="14"/>
       <c r="BV1" s="4"/>
       <c r="BW1" s="4"/>
       <c r="BX1" s="4"/>
     </row>
     <row r="2" spans="1:76" ht="4.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="1:76" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="14" t="s">
+      <c r="A3" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="14"/>
-      <c r="C3" s="14"/>
-      <c r="D3" s="14"/>
-      <c r="E3" s="14"/>
-      <c r="F3" s="14"/>
-      <c r="G3" s="14"/>
-      <c r="H3" s="14"/>
-      <c r="I3" s="14"/>
-      <c r="J3" s="14"/>
-      <c r="K3" s="14"/>
-      <c r="L3" s="14"/>
-      <c r="M3" s="14"/>
-      <c r="N3" s="14"/>
-      <c r="O3" s="14"/>
-      <c r="P3" s="14"/>
-      <c r="Q3" s="14"/>
-      <c r="R3" s="14"/>
-      <c r="S3" s="14"/>
-      <c r="T3" s="14"/>
-      <c r="U3" s="14"/>
-      <c r="V3" s="14"/>
-      <c r="W3" s="14"/>
-      <c r="X3" s="14"/>
-      <c r="Y3" s="14"/>
-      <c r="Z3" s="14"/>
-      <c r="AA3" s="14"/>
-      <c r="AB3" s="14"/>
-      <c r="AC3" s="14"/>
-      <c r="AD3" s="14"/>
-      <c r="AE3" s="14"/>
-      <c r="AF3" s="14"/>
-      <c r="AG3" s="14"/>
-      <c r="AH3" s="14"/>
-      <c r="AI3" s="14"/>
-      <c r="AJ3" s="14"/>
-      <c r="AK3" s="14"/>
-      <c r="AL3" s="14"/>
-      <c r="AM3" s="14"/>
-      <c r="AN3" s="14"/>
-      <c r="AO3" s="14"/>
-      <c r="AP3" s="14"/>
-      <c r="AQ3" s="14"/>
-      <c r="AR3" s="14"/>
-      <c r="AS3" s="14"/>
-      <c r="AT3" s="14"/>
-      <c r="AU3" s="14"/>
-      <c r="AV3" s="14"/>
-      <c r="AW3" s="14"/>
-      <c r="AX3" s="14"/>
-      <c r="AY3" s="14"/>
-      <c r="AZ3" s="14"/>
-      <c r="BA3" s="14"/>
-      <c r="BB3" s="14"/>
-      <c r="BC3" s="14"/>
-      <c r="BD3" s="14"/>
-      <c r="BE3" s="14"/>
-      <c r="BF3" s="14"/>
-      <c r="BG3" s="14"/>
-      <c r="BH3" s="14"/>
-      <c r="BI3" s="14"/>
-      <c r="BJ3" s="14"/>
-      <c r="BK3" s="14"/>
-      <c r="BL3" s="14"/>
-      <c r="BM3" s="14"/>
-      <c r="BN3" s="14"/>
-      <c r="BO3" s="14"/>
-      <c r="BP3" s="14"/>
-      <c r="BQ3" s="14"/>
-      <c r="BR3" s="14"/>
-      <c r="BS3" s="14"/>
-      <c r="BT3" s="14"/>
-      <c r="BU3" s="14"/>
-      <c r="BV3" s="14"/>
-      <c r="BW3" s="14"/>
-      <c r="BX3" s="14"/>
+      <c r="B3" s="9"/>
+      <c r="C3" s="9"/>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="9"/>
+      <c r="I3" s="9"/>
+      <c r="J3" s="9"/>
+      <c r="K3" s="9"/>
+      <c r="L3" s="9"/>
+      <c r="M3" s="9"/>
+      <c r="N3" s="9"/>
+      <c r="O3" s="9"/>
+      <c r="P3" s="9"/>
+      <c r="Q3" s="9"/>
+      <c r="R3" s="9"/>
+      <c r="S3" s="9"/>
+      <c r="T3" s="9"/>
+      <c r="U3" s="9"/>
+      <c r="V3" s="9"/>
+      <c r="W3" s="9"/>
+      <c r="X3" s="9"/>
+      <c r="Y3" s="9"/>
+      <c r="Z3" s="9"/>
+      <c r="AA3" s="9"/>
+      <c r="AB3" s="9"/>
+      <c r="AC3" s="9"/>
+      <c r="AD3" s="9"/>
+      <c r="AE3" s="9"/>
+      <c r="AF3" s="9"/>
+      <c r="AG3" s="9"/>
+      <c r="AH3" s="9"/>
+      <c r="AI3" s="9"/>
+      <c r="AJ3" s="9"/>
+      <c r="AK3" s="9"/>
+      <c r="AL3" s="9"/>
+      <c r="AM3" s="9"/>
+      <c r="AN3" s="9"/>
+      <c r="AO3" s="9"/>
+      <c r="AP3" s="9"/>
+      <c r="AQ3" s="9"/>
+      <c r="AR3" s="9"/>
+      <c r="AS3" s="9"/>
+      <c r="AT3" s="9"/>
+      <c r="AU3" s="9"/>
+      <c r="AV3" s="9"/>
+      <c r="AW3" s="9"/>
+      <c r="AX3" s="9"/>
+      <c r="AY3" s="9"/>
+      <c r="AZ3" s="9"/>
+      <c r="BA3" s="9"/>
+      <c r="BB3" s="9"/>
+      <c r="BC3" s="9"/>
+      <c r="BD3" s="9"/>
+      <c r="BE3" s="9"/>
+      <c r="BF3" s="9"/>
+      <c r="BG3" s="9"/>
+      <c r="BH3" s="9"/>
+      <c r="BI3" s="9"/>
+      <c r="BJ3" s="9"/>
+      <c r="BK3" s="9"/>
+      <c r="BL3" s="9"/>
+      <c r="BM3" s="9"/>
+      <c r="BN3" s="9"/>
+      <c r="BO3" s="9"/>
+      <c r="BP3" s="9"/>
+      <c r="BQ3" s="9"/>
+      <c r="BR3" s="9"/>
+      <c r="BS3" s="9"/>
+      <c r="BT3" s="9"/>
+      <c r="BU3" s="9"/>
+      <c r="BV3" s="9"/>
+      <c r="BW3" s="9"/>
+      <c r="BX3" s="9"/>
     </row>
     <row r="4" spans="1:76" ht="3" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="5" spans="1:76" x14ac:dyDescent="0.25">
-      <c r="A5" s="15" t="s">
+      <c r="A5" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="15"/>
-      <c r="C5" s="15"/>
-      <c r="D5" s="15"/>
-      <c r="E5" s="15"/>
-      <c r="F5" s="15"/>
-      <c r="G5" s="15"/>
-      <c r="H5" s="15"/>
-      <c r="I5" s="15"/>
-      <c r="J5" s="15"/>
-      <c r="K5" s="15"/>
-      <c r="W5" s="17" t="s">
+      <c r="B5" s="10"/>
+      <c r="C5" s="10"/>
+      <c r="D5" s="10"/>
+      <c r="E5" s="10"/>
+      <c r="F5" s="10"/>
+      <c r="G5" s="10"/>
+      <c r="H5" s="10"/>
+      <c r="I5" s="10"/>
+      <c r="J5" s="10"/>
+      <c r="K5" s="10"/>
+      <c r="W5" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="X5" s="17"/>
-      <c r="Y5" s="17"/>
-      <c r="Z5" s="17"/>
-      <c r="AA5" s="17"/>
-      <c r="AB5" s="17"/>
-      <c r="AC5" s="17"/>
-      <c r="AD5" s="17"/>
-      <c r="AE5" s="17"/>
-      <c r="AF5" s="17"/>
-      <c r="AG5" s="17"/>
-      <c r="AH5" s="17"/>
-      <c r="AI5" s="17"/>
-      <c r="AJ5" s="17"/>
-      <c r="AK5" s="17"/>
-      <c r="AL5" s="17"/>
-      <c r="AM5" s="17"/>
-      <c r="AN5" s="17"/>
-      <c r="AO5" s="17"/>
-      <c r="AP5" s="17"/>
-      <c r="AQ5" s="17"/>
-      <c r="AR5" s="17"/>
-      <c r="AS5" s="17"/>
-      <c r="AT5" s="17"/>
-      <c r="AU5" s="17"/>
+      <c r="X5" s="12"/>
+      <c r="Y5" s="12"/>
+      <c r="Z5" s="12"/>
+      <c r="AA5" s="12"/>
+      <c r="AB5" s="12"/>
+      <c r="AC5" s="12"/>
+      <c r="AD5" s="12"/>
+      <c r="AE5" s="12"/>
+      <c r="AF5" s="12"/>
+      <c r="AG5" s="12"/>
+      <c r="AH5" s="12"/>
+      <c r="AI5" s="12"/>
+      <c r="AJ5" s="12"/>
+      <c r="AK5" s="12"/>
+      <c r="AL5" s="12"/>
+      <c r="AM5" s="12"/>
+      <c r="AN5" s="12"/>
+      <c r="AO5" s="12"/>
+      <c r="AP5" s="12"/>
+      <c r="AQ5" s="12"/>
+      <c r="AR5" s="12"/>
+      <c r="AS5" s="12"/>
+      <c r="AT5" s="12"/>
+      <c r="AU5" s="12"/>
     </row>
     <row r="6" spans="1:76" x14ac:dyDescent="0.25">
-      <c r="A6" s="16" t="s">
+      <c r="A6" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="B6" s="16"/>
-      <c r="C6" s="16"/>
-      <c r="D6" s="16"/>
-      <c r="E6" s="16"/>
-      <c r="F6" s="16"/>
-      <c r="G6" s="16"/>
-      <c r="H6" s="16"/>
-      <c r="I6" s="16"/>
-      <c r="J6" s="16"/>
-      <c r="K6" s="16"/>
-      <c r="L6" s="16"/>
-      <c r="M6" s="16"/>
-      <c r="N6" s="16"/>
-      <c r="O6" s="16"/>
-      <c r="P6" s="16"/>
-      <c r="Q6" s="16"/>
-      <c r="W6" s="17" t="s">
+      <c r="B6" s="11"/>
+      <c r="C6" s="11"/>
+      <c r="D6" s="11"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="11"/>
+      <c r="J6" s="11"/>
+      <c r="K6" s="11"/>
+      <c r="L6" s="11"/>
+      <c r="M6" s="11"/>
+      <c r="N6" s="11"/>
+      <c r="O6" s="11"/>
+      <c r="P6" s="11"/>
+      <c r="Q6" s="11"/>
+      <c r="W6" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="X6" s="17"/>
-      <c r="Y6" s="17"/>
-      <c r="Z6" s="17"/>
-      <c r="AA6" s="17"/>
-      <c r="AB6" s="17"/>
-      <c r="AC6" s="17"/>
-      <c r="AD6" s="17"/>
-      <c r="AE6" s="17"/>
-      <c r="AF6" s="17"/>
-      <c r="AG6" s="17"/>
-      <c r="AH6" s="17"/>
-      <c r="AI6" s="17"/>
-      <c r="AJ6" s="17"/>
-      <c r="AK6" s="17"/>
-      <c r="AL6" s="17"/>
-      <c r="AM6" s="17"/>
-      <c r="AN6" s="17"/>
-      <c r="AO6" s="17"/>
-      <c r="AP6" s="17"/>
-      <c r="AQ6" s="17"/>
-      <c r="AR6" s="17" t="s">
+      <c r="X6" s="12"/>
+      <c r="Y6" s="12"/>
+      <c r="Z6" s="12"/>
+      <c r="AA6" s="12"/>
+      <c r="AB6" s="12"/>
+      <c r="AC6" s="12"/>
+      <c r="AD6" s="12"/>
+      <c r="AE6" s="12"/>
+      <c r="AF6" s="12"/>
+      <c r="AG6" s="12"/>
+      <c r="AH6" s="12"/>
+      <c r="AI6" s="12"/>
+      <c r="AJ6" s="12"/>
+      <c r="AK6" s="12"/>
+      <c r="AL6" s="12"/>
+      <c r="AM6" s="12"/>
+      <c r="AN6" s="12"/>
+      <c r="AO6" s="12"/>
+      <c r="AP6" s="12"/>
+      <c r="AQ6" s="12"/>
+      <c r="AR6" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="AS6" s="17"/>
-      <c r="AT6" s="17"/>
-      <c r="AU6" s="17"/>
-      <c r="AV6" s="17"/>
-      <c r="AW6" s="17"/>
-      <c r="AX6" s="17"/>
-      <c r="AY6" s="17"/>
-      <c r="AZ6" s="17"/>
-      <c r="BA6" s="17"/>
-      <c r="BB6" s="17"/>
-      <c r="BC6" s="17"/>
-      <c r="BD6" s="17"/>
+      <c r="AS6" s="12"/>
+      <c r="AT6" s="12"/>
+      <c r="AU6" s="12"/>
+      <c r="AV6" s="12"/>
+      <c r="AW6" s="12"/>
+      <c r="AX6" s="12"/>
+      <c r="AY6" s="12"/>
+      <c r="AZ6" s="12"/>
+      <c r="BA6" s="12"/>
+      <c r="BB6" s="12"/>
+      <c r="BC6" s="12"/>
+      <c r="BD6" s="12"/>
     </row>
     <row r="8" spans="1:76" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="13" t="s">
+      <c r="A8" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="B8" s="13"/>
+      <c r="B8" s="8"/>
     </row>
     <row r="9" spans="1:76" x14ac:dyDescent="0.25">
-      <c r="A9" s="13"/>
-      <c r="B9" s="13"/>
+      <c r="A9" s="8"/>
+      <c r="B9" s="8"/>
     </row>
     <row r="10" spans="1:76" x14ac:dyDescent="0.25">
-      <c r="A10" s="13"/>
-      <c r="B10" s="13"/>
+      <c r="A10" s="8"/>
+      <c r="B10" s="8"/>
     </row>
     <row r="11" spans="1:76" x14ac:dyDescent="0.25">
-      <c r="A11" s="13"/>
-      <c r="B11" s="13"/>
+      <c r="A11" s="8"/>
+      <c r="B11" s="8"/>
     </row>
     <row r="12" spans="1:76" x14ac:dyDescent="0.25">
-      <c r="A12" s="13"/>
-      <c r="B12" s="13"/>
+      <c r="A12" s="8"/>
+      <c r="B12" s="8"/>
     </row>
     <row r="13" spans="1:76" x14ac:dyDescent="0.25">
-      <c r="A13" s="13"/>
-      <c r="B13" s="13"/>
+      <c r="A13" s="8"/>
+      <c r="B13" s="8"/>
     </row>
     <row r="14" spans="1:76" x14ac:dyDescent="0.25">
-      <c r="A14" s="13"/>
-      <c r="B14" s="13"/>
+      <c r="A14" s="8"/>
+      <c r="B14" s="8"/>
     </row>
     <row r="15" spans="1:76" x14ac:dyDescent="0.25">
-      <c r="A15" s="13"/>
-      <c r="B15" s="13"/>
+      <c r="A15" s="8"/>
+      <c r="B15" s="8"/>
     </row>
     <row r="16" spans="1:76" x14ac:dyDescent="0.25">
-      <c r="A16" s="13"/>
-      <c r="B16" s="13"/>
+      <c r="A16" s="8"/>
+      <c r="B16" s="8"/>
     </row>
     <row r="17" spans="1:77" x14ac:dyDescent="0.25">
-      <c r="A17" s="13"/>
-      <c r="B17" s="13"/>
+      <c r="A17" s="8"/>
+      <c r="B17" s="8"/>
     </row>
     <row r="18" spans="1:77" x14ac:dyDescent="0.25">
-      <c r="A18" s="13"/>
-      <c r="B18" s="13"/>
+      <c r="A18" s="8"/>
+      <c r="B18" s="8"/>
     </row>
     <row r="19" spans="1:77" x14ac:dyDescent="0.25">
-      <c r="A19" s="13"/>
-      <c r="B19" s="13"/>
+      <c r="A19" s="8"/>
+      <c r="B19" s="8"/>
     </row>
     <row r="20" spans="1:77" x14ac:dyDescent="0.25">
-      <c r="A20" s="13"/>
-      <c r="B20" s="13"/>
+      <c r="A20" s="8"/>
+      <c r="B20" s="8"/>
     </row>
     <row r="21" spans="1:77" x14ac:dyDescent="0.25">
-      <c r="A21" s="13"/>
-      <c r="B21" s="13"/>
+      <c r="A21" s="8"/>
+      <c r="B21" s="8"/>
     </row>
     <row r="22" spans="1:77" x14ac:dyDescent="0.25">
-      <c r="A22" s="13"/>
-      <c r="B22" s="13"/>
+      <c r="A22" s="8"/>
+      <c r="B22" s="8"/>
     </row>
     <row r="23" spans="1:77" x14ac:dyDescent="0.25">
-      <c r="A23" s="13"/>
-      <c r="B23" s="13"/>
+      <c r="A23" s="8"/>
+      <c r="B23" s="8"/>
     </row>
     <row r="24" spans="1:77" x14ac:dyDescent="0.25">
-      <c r="A24" s="13"/>
-      <c r="B24" s="13"/>
+      <c r="A24" s="8"/>
+      <c r="B24" s="8"/>
     </row>
     <row r="25" spans="1:77" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
@@ -1069,106 +1069,103 @@
     </row>
     <row r="27" spans="1:77" x14ac:dyDescent="0.25">
       <c r="A27" s="1"/>
-      <c r="BY27">
-        <v>36</v>
-      </c>
     </row>
     <row r="28" spans="1:77" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
-      <c r="B28" s="13"/>
-      <c r="C28" s="13"/>
-      <c r="D28" s="13"/>
-      <c r="E28" s="13"/>
-      <c r="F28" s="13"/>
-      <c r="G28" s="13"/>
+      <c r="B28" s="8"/>
+      <c r="C28" s="8"/>
+      <c r="D28" s="8"/>
+      <c r="E28" s="8"/>
+      <c r="F28" s="8"/>
+      <c r="G28" s="8"/>
     </row>
     <row r="29" spans="1:77" ht="5.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1"/>
-      <c r="B29" s="13"/>
-      <c r="C29" s="13"/>
-      <c r="D29" s="13"/>
-      <c r="E29" s="13"/>
-      <c r="F29" s="13"/>
-      <c r="G29" s="13"/>
+      <c r="B29" s="8"/>
+      <c r="C29" s="8"/>
+      <c r="D29" s="8"/>
+      <c r="E29" s="8"/>
+      <c r="F29" s="8"/>
+      <c r="G29" s="8"/>
     </row>
     <row r="30" spans="1:77" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
       <c r="F30" s="7"/>
       <c r="G30" s="7"/>
-      <c r="H30" s="9" t="s">
+      <c r="H30" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="I30" s="9"/>
+      <c r="I30" s="6"/>
       <c r="J30" s="5" t="s">
         <v>9</v>
       </c>
       <c r="K30" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="L30" s="9" t="s">
+      <c r="L30" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M30" s="9"/>
-      <c r="N30" s="9" t="s">
+      <c r="M30" s="6"/>
+      <c r="N30" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="O30" s="9"/>
-      <c r="P30" s="9" t="s">
+      <c r="O30" s="6"/>
+      <c r="P30" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="Q30" s="9"/>
-      <c r="R30" s="9" t="s">
+      <c r="Q30" s="6"/>
+      <c r="R30" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="S30" s="9"/>
-      <c r="T30" s="9" t="s">
+      <c r="S30" s="6"/>
+      <c r="T30" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="U30" s="9"/>
-      <c r="V30" s="9" t="s">
+      <c r="U30" s="6"/>
+      <c r="V30" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="W30" s="9"/>
-      <c r="X30" s="9" t="s">
+      <c r="W30" s="6"/>
+      <c r="X30" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="Y30" s="9"/>
-      <c r="Z30" s="9" t="s">
+      <c r="Y30" s="6"/>
+      <c r="Z30" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="AA30" s="9"/>
-      <c r="AB30" s="9" t="s">
+      <c r="AA30" s="6"/>
+      <c r="AB30" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="AC30" s="9"/>
-      <c r="AD30" s="9" t="s">
+      <c r="AC30" s="6"/>
+      <c r="AD30" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="AE30" s="9"/>
-      <c r="AF30" s="9" t="s">
+      <c r="AE30" s="6"/>
+      <c r="AF30" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="AG30" s="9"/>
-      <c r="AH30" s="9" t="s">
+      <c r="AG30" s="6"/>
+      <c r="AH30" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="AI30" s="9"/>
-      <c r="AJ30" s="9" t="s">
+      <c r="AI30" s="6"/>
+      <c r="AJ30" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="AK30" s="9"/>
-      <c r="AL30" s="9" t="s">
+      <c r="AK30" s="6"/>
+      <c r="AL30" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="AM30" s="9"/>
-      <c r="AN30" s="9" t="s">
+      <c r="AM30" s="6"/>
+      <c r="AN30" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="AO30" s="9"/>
-      <c r="AP30" s="9" t="s">
+      <c r="AO30" s="6"/>
+      <c r="AP30" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="AQ30" s="9"/>
+      <c r="AQ30" s="6"/>
       <c r="AR30" s="5" t="s">
         <v>27</v>
       </c>
@@ -1229,30 +1226,30 @@
       <c r="BK30" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="BL30" s="9" t="s">
+      <c r="BL30" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="BM30" s="9"/>
-      <c r="BN30" s="9" t="s">
+      <c r="BM30" s="6"/>
+      <c r="BN30" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="BO30" s="9"/>
-      <c r="BP30" s="9" t="s">
+      <c r="BO30" s="6"/>
+      <c r="BP30" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="BQ30" s="9"/>
-      <c r="BR30" s="9" t="s">
+      <c r="BQ30" s="6"/>
+      <c r="BR30" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="BS30" s="9"/>
-      <c r="BT30" s="9" t="s">
+      <c r="BS30" s="6"/>
+      <c r="BT30" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="BU30" s="9"/>
-      <c r="BV30" s="10"/>
-      <c r="BW30" s="10"/>
-      <c r="BX30" s="10"/>
-      <c r="BY30" s="10"/>
+      <c r="BU30" s="6"/>
+      <c r="BV30" s="13"/>
+      <c r="BW30" s="13"/>
+      <c r="BX30" s="13"/>
+      <c r="BY30" s="13"/>
     </row>
     <row r="31" spans="1:77" x14ac:dyDescent="0.25">
       <c r="A31" s="1"/>
@@ -1404,20 +1401,45 @@
       <c r="BU33" s="7"/>
     </row>
     <row r="36" spans="1:73" x14ac:dyDescent="0.25">
-      <c r="A36" s="8"/>
-      <c r="B36" s="8"/>
-      <c r="C36" s="8"/>
-      <c r="D36" s="8"/>
-      <c r="E36" s="8"/>
-      <c r="F36" s="8"/>
-      <c r="G36" s="8"/>
-      <c r="H36" s="8"/>
-      <c r="I36" s="8"/>
-      <c r="J36" s="8"/>
-      <c r="K36" s="8"/>
+      <c r="A36" s="15"/>
+      <c r="B36" s="15"/>
+      <c r="C36" s="15"/>
+      <c r="D36" s="15"/>
+      <c r="E36" s="15"/>
+      <c r="F36" s="15"/>
+      <c r="G36" s="15"/>
+      <c r="H36" s="15"/>
+      <c r="I36" s="15"/>
+      <c r="J36" s="15"/>
+      <c r="K36" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="41">
+    <mergeCell ref="BJ1:BU1"/>
+    <mergeCell ref="BL31:BU31"/>
+    <mergeCell ref="AD32:BU32"/>
+    <mergeCell ref="AD33:BU33"/>
+    <mergeCell ref="A36:K36"/>
+    <mergeCell ref="BN30:BO30"/>
+    <mergeCell ref="BP30:BQ30"/>
+    <mergeCell ref="BR30:BS30"/>
+    <mergeCell ref="BT30:BU30"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="AD1:AT1"/>
+    <mergeCell ref="AD30:AE30"/>
+    <mergeCell ref="H30:I30"/>
+    <mergeCell ref="L30:M30"/>
+    <mergeCell ref="N30:O30"/>
+    <mergeCell ref="P30:Q30"/>
+    <mergeCell ref="BV30:BW30"/>
+    <mergeCell ref="BX30:BY30"/>
+    <mergeCell ref="BL30:BM30"/>
+    <mergeCell ref="AP30:AQ30"/>
+    <mergeCell ref="AF30:AG30"/>
+    <mergeCell ref="AH30:AI30"/>
+    <mergeCell ref="AJ30:AK30"/>
+    <mergeCell ref="AL30:AM30"/>
+    <mergeCell ref="AN30:AO30"/>
     <mergeCell ref="AB30:AC30"/>
     <mergeCell ref="F30:G30"/>
     <mergeCell ref="B29:G29"/>
@@ -1434,31 +1456,6 @@
     <mergeCell ref="V30:W30"/>
     <mergeCell ref="X30:Y30"/>
     <mergeCell ref="Z30:AA30"/>
-    <mergeCell ref="BV30:BW30"/>
-    <mergeCell ref="BX30:BY30"/>
-    <mergeCell ref="BL30:BM30"/>
-    <mergeCell ref="AP30:AQ30"/>
-    <mergeCell ref="AF30:AG30"/>
-    <mergeCell ref="AH30:AI30"/>
-    <mergeCell ref="AJ30:AK30"/>
-    <mergeCell ref="AL30:AM30"/>
-    <mergeCell ref="AN30:AO30"/>
-    <mergeCell ref="BJ1:BU1"/>
-    <mergeCell ref="BL31:BU31"/>
-    <mergeCell ref="AD32:BU32"/>
-    <mergeCell ref="AD33:BU33"/>
-    <mergeCell ref="A36:K36"/>
-    <mergeCell ref="BN30:BO30"/>
-    <mergeCell ref="BP30:BQ30"/>
-    <mergeCell ref="BR30:BS30"/>
-    <mergeCell ref="BT30:BU30"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="AD1:AT1"/>
-    <mergeCell ref="AD30:AE30"/>
-    <mergeCell ref="H30:I30"/>
-    <mergeCell ref="L30:M30"/>
-    <mergeCell ref="N30:O30"/>
-    <mergeCell ref="P30:Q30"/>
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
